--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileEstimatedBillTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileEstimatedBillTemplate.xlsx
@@ -34,7 +34,19 @@
     <t>业务单号</t>
   </si>
   <si>
-    <t>物流运单号</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>物流运单号</t>
+    </r>
   </si>
   <si>
     <t>来源单号</t>
@@ -44,6 +56,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -59,6 +78,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1057,7 +1083,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">

--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileEstimatedBillTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileEstimatedBillTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>业务单号</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -98,6 +105,20 @@
       <t>预付费用</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>币种</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -109,7 +130,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -273,6 +294,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1068,8 +1095,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="14.25" customWidth="1"/>
     <col min="2" max="2" width="14.5" customWidth="1"/>
@@ -1079,7 +1106,7 @@
     <col min="6" max="6" width="12.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1" spans="1:6">
+    <row r="1" ht="16" customHeight="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1097,6 +1124,9 @@
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileEstimatedBillTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileEstimatedBillTemplate.xlsx
@@ -29,37 +29,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>业务单号</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>物流运单号</t>
-    </r>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>来源单号</t>
   </si>
   <si>
-    <t>物流跟踪号</t>
+    <t>物流运单号</t>
+  </si>
+  <si>
+    <t>业务单号</t>
   </si>
   <si>
     <r>
@@ -107,6 +85,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1095,28 +1080,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14.25" customWidth="1"/>
     <col min="2" max="2" width="14.5" customWidth="1"/>
     <col min="3" max="3" width="14.625" customWidth="1"/>
-    <col min="4" max="4" width="14.75" customWidth="1"/>
-    <col min="5" max="5" width="13.125" customWidth="1"/>
-    <col min="6" max="6" width="12.375" customWidth="1"/>
+    <col min="4" max="4" width="13.125" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1" spans="1:7">
+    <row r="1" ht="16" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -1124,9 +1108,6 @@
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
